--- a/Take-Home_Ex/Take_home_Ex02/Total_Merchandise_Trade_201525.xlsx
+++ b/Take-Home_Ex/Take_home_Ex02/Total_Merchandise_Trade_201525.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947487E4-D45F-45E3-9FBD-73B6410869C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E30668E-479C-49FD-B786-3CE25D5EE270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="750" yWindow="5460" windowWidth="21420" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="75" yWindow="0" windowWidth="22178" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M451001" sheetId="1" r:id="rId1"/>
@@ -383,19 +383,20 @@
     <t xml:space="preserve">2015 Jan </t>
   </si>
   <si>
+    <t>Total Merchandise Imports, (At Current Prices)</t>
+  </si>
+  <si>
+    <t>Total Merchandise Exports, (At Current Prices)</t>
+  </si>
+  <si>
+    <t>Total Domestic Exports, (At Current Prices)</t>
+  </si>
+  <si>
+    <t>Total Re-Exports, (At Current Prices)</t>
+  </si>
+  <si>
     <t>Total Merchandise Trade, (At Current Prices)</t>
-  </si>
-  <si>
-    <t>Total Merchandise Imports, (At Current Prices)</t>
-  </si>
-  <si>
-    <t>Total Merchandise Exports, (At Current Prices)</t>
-  </si>
-  <si>
-    <t>Total Domestic Exports, (At Current Prices)</t>
-  </si>
-  <si>
-    <t>Total Re-Exports, (At Current Prices)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1192,7 +1193,7 @@
     </row>
     <row r="2" spans="1:122">
       <c r="A2" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B2" s="4">
         <v>114153979.90000001</v>
@@ -1560,7 +1561,7 @@
     </row>
     <row r="3" spans="1:122">
       <c r="A3" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3" s="4">
         <v>54746365.700000003</v>
@@ -1928,7 +1929,7 @@
     </row>
     <row r="4" spans="1:122">
       <c r="A4" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B4" s="4">
         <v>59407614.200000003</v>
@@ -2296,7 +2297,7 @@
     </row>
     <row r="5" spans="1:122">
       <c r="A5" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B5" s="4">
         <v>24671972.800000001</v>
@@ -2664,7 +2665,7 @@
     </row>
     <row r="6" spans="1:122">
       <c r="A6" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B6" s="4">
         <v>34735641.399999999</v>
